--- a/data/gated_research/npb.xlsx
+++ b/data/gated_research/npb.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CP$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -979,6 +979,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1447,9 +1448,14 @@
           <t>schedule_missingness</t>
         </is>
       </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
+  <autoFilter ref="A1:CP1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/gated_research/npb.xlsx
+++ b/data/gated_research/npb.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CP$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CQ$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP1"/>
+  <dimension ref="A1:CQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -979,7 +979,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1450,12 +1451,17 @@
       </c>
       <c r="CP1" s="23" t="inlineStr">
         <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
+        <is>
           <t>trade_candidate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CP1"/>
+  <autoFilter ref="A1:CQ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/gated_research/npb.xlsx
+++ b/data/gated_research/npb.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CQ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CR$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ1"/>
+  <dimension ref="A1:CR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -975,12 +975,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1431,37 +1432,42 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CQ1"/>
+  <autoFilter ref="A1:CR1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/gated_research/npb.xlsx
+++ b/data/gated_research/npb.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CR$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CS$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR1"/>
+  <dimension ref="A1:CS1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -976,12 +976,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1437,37 +1438,42 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CR1"/>
+  <autoFilter ref="A1:CS1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/gated_research/npb.xlsx
+++ b/data/gated_research/npb.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CS$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,112 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS2" headerRowCount="1">
+  <autoFilter ref="A1:CS2"/>
+  <tableColumns count="97">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -883,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS1"/>
+  <dimension ref="A1:CS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1472,9 +1603,280 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>926c19c9195543cd</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.605094</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.055544</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="n"/>
+      <c r="W2" s="26" t="n"/>
+      <c r="X2" s="26" t="n"/>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n"/>
+      <c r="AD2" s="24" t="n"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-cdh-tys-2026-08-05). Tie probability=0.0272.</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.865696Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CS1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/gated_research/npb.xlsx
+++ b/data/gated_research/npb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -1684,18 +1684,32 @@
       </c>
       <c r="U2" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="24" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>1.0246</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:32.134597Z</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-cdh-tys-2026-08-05). Tie probability=0.0272.</t>

--- a/data/gated_research/npb.xlsx
+++ b/data/gated_research/npb.xlsx
@@ -1,18 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CS$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,112 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS3" headerRowCount="1">
+  <autoFilter ref="A1:CS3"/>
+  <tableColumns count="97">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$3)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$3,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")/(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$3)/SUM('Picks'!$BX$2:$BX$3),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$3)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$3,"&lt;&gt;",'Picks'!$AB$2:$AB$3),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$3,'Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS1"/>
+  <dimension ref="A1:CS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1472,9 +1603,577 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>926c19c9195543cd</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.605094</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.055544</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>1.0246</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:32.134597Z</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-cdh-tys-2026-08-05). Tie probability=0.0272.</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.865696Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>a157cb3f9245401f</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014675Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>72695</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.657907</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>0.098436</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>1.378</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:17.941486Z</t>
+        </is>
+      </c>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-ygo-tys-2026-08-08). Tie probability=0.0222.</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:47.516040Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CS1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>